--- a/exports/templates/importacion/template_importacion_salones_minimo.xlsx
+++ b/exports/templates/importacion/template_importacion_salones_minimo.xlsx
@@ -12,15 +12,33 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
-  <si>
-    <t>Salon</t>
-  </si>
-  <si>
-    <t>A101 (Central)</t>
-  </si>
-  <si>
-    <t>Lab 2 (Ciencias)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="23">
+  <si>
+    <t>Nombre salon</t>
+  </si>
+  <si>
+    <t>Edificio</t>
+  </si>
+  <si>
+    <t>Aforo</t>
+  </si>
+  <si>
+    <t>A101</t>
+  </si>
+  <si>
+    <t>Central</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>Lab 2</t>
+  </si>
+  <si>
+    <t>Ciencias</t>
+  </si>
+  <si>
+    <t>35</t>
   </si>
   <si>
     <t>Template: Importacion salones (Minimo)</t>
@@ -53,10 +71,16 @@
     <t>Estado</t>
   </si>
   <si>
-    <t>Ej: A101 (Central)</t>
+    <t>Nombre del salon (tabla salones.nombre)</t>
   </si>
   <si>
     <t>Obligatorio</t>
+  </si>
+  <si>
+    <t>Edificio del salon (tabla salones.edificio)</t>
+  </si>
+  <si>
+    <t>Aforo del salon (tabla salones.aforo)</t>
   </si>
 </sst>
 </file>
@@ -462,25 +486,44 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="3" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -491,7 +534,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -501,44 +544,44 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -546,10 +589,32 @@
         <v>0</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>14</v>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
